--- a/gempa_diraskan_PGR3_UTC.xlsx
+++ b/gempa_diraskan_PGR3_UTC.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Seismioto\Pengolahan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9324BACD-69BE-4C9D-B5D8-D20EA0232EFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60064238-BE13-41D4-A366-CFD0579E8184}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2856" yWindow="2856" windowWidth="7500" windowHeight="9456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet2" sheetId="2" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="20">
   <si>
     <t>Tanggal</t>
   </si>
@@ -60,54 +60,66 @@
     <t>Dirasakan</t>
   </si>
   <si>
-    <t>22 km Tenggara Karangasem-Bali</t>
-  </si>
-  <si>
-    <t>dirasakan di wilayah Kab. Karangasem III MMI</t>
-  </si>
-  <si>
-    <t>9 km Barat Daya Dompu-NTB</t>
-  </si>
-  <si>
     <t>dirasakan di wilayah Sumbawa Besar III MMI, Kota Bima II MMI</t>
   </si>
   <si>
-    <t>29 km Timur Laut Lombok Utara-NTB</t>
-  </si>
-  <si>
     <t>dirasakan di wilayah Lombok Timur II-III MMI</t>
   </si>
   <si>
-    <t>70 km Tenggara Kuta Selatan-Bali</t>
-  </si>
-  <si>
-    <t>dirasakan di wilayah Kuta, Kuta Selatan, Klungkung, Lombok Barat, dan Lombok Tengah II MMI</t>
-  </si>
-  <si>
-    <t>78 km Utara Sumbawa-NTB</t>
-  </si>
-  <si>
-    <t>dirasakan di wilayah Kab. Sumbawa Barat, Kab. Sumbawa, Kab. Bima, dan Kab. Lombok Timur II MMI</t>
-  </si>
-  <si>
     <t>Waktu (UTC)</t>
+  </si>
+  <si>
+    <t>Bali Region, Indonesia</t>
+  </si>
+  <si>
+    <t>dirasakan di wilayah Kab Karangasem III MMI</t>
+  </si>
+  <si>
+    <t>South of Sumbawa, Indonesia</t>
+  </si>
+  <si>
+    <t>dirasakan di daerah Kodi Sumba Barat Daya I-II MMI</t>
+  </si>
+  <si>
+    <t>South of Bali, Indonesia</t>
+  </si>
+  <si>
+    <t>dirasakan di wilayah Kuta dan Kuta Selatan II MMI</t>
+  </si>
+  <si>
+    <t>Sumbawa Region, Indonesia</t>
+  </si>
+  <si>
+    <t>dirasakan di wilayah Kuta, Kuta Selatan, dan Klungkung II MMI</t>
+  </si>
+  <si>
+    <t>Bali Sea</t>
+  </si>
+  <si>
+    <t>dirasakan di wilayah Kabupaten Sumbawa Barat, Kabupaten Sumbawa, Kabupaten Bima, dan Kabupaten Lombok Timur II MMI</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd;@"/>
     <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="166" formatCode="0.0"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
     </font>
     <font>
       <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -132,16 +144,31 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="21" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="21" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -458,206 +485,253 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{822B08B2-1387-4C99-A9BB-7378259DE79F}">
   <dimension ref="A1:H17"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="10.6640625" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.5546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="7" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="17.44140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.33203125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="36.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="159" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.44140625" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="36.5546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="159" style="2" bestFit="1" customWidth="1"/>
+    <col min="9" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
-      <c r="A1" t="s">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2" s="6">
+        <v>46054</v>
+      </c>
+      <c r="B2" s="7">
+        <v>0.56193287037037032</v>
+      </c>
+      <c r="C2" s="8">
+        <v>-8.4597999999999995</v>
+      </c>
+      <c r="D2" s="8">
+        <v>115.68380000000001</v>
+      </c>
+      <c r="E2" s="10">
+        <v>11.2</v>
+      </c>
+      <c r="F2" s="8">
+        <v>3.55</v>
+      </c>
+      <c r="G2" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="H2" s="8" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3" s="6">
+        <v>46068</v>
+      </c>
+      <c r="B3" s="7">
+        <v>0.57231481481481483</v>
+      </c>
+      <c r="C3" s="8">
+        <v>-11.37</v>
+      </c>
+      <c r="D3" s="8">
+        <v>118.04</v>
+      </c>
+      <c r="E3" s="10">
+        <v>10</v>
+      </c>
+      <c r="F3" s="9">
+        <v>5</v>
+      </c>
+      <c r="G3" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="H3" s="8" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A4" s="6">
+        <v>46069</v>
+      </c>
+      <c r="B4" s="7">
+        <v>0.80798611111111107</v>
+      </c>
+      <c r="C4" s="8">
+        <v>-9.2272999999999996</v>
+      </c>
+      <c r="D4" s="8">
+        <v>114.69</v>
+      </c>
+      <c r="E4" s="10">
+        <v>84.2</v>
+      </c>
+      <c r="F4" s="8">
+        <v>4.01</v>
+      </c>
+      <c r="G4" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="H4" s="8" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A5" s="6">
+        <v>46069</v>
+      </c>
+      <c r="B5" s="7">
+        <v>0.48768518518518517</v>
+      </c>
+      <c r="C5" s="8">
+        <v>-8.5641999999999996</v>
+      </c>
+      <c r="D5" s="8">
+        <v>118.383</v>
+      </c>
+      <c r="E5" s="10">
+        <v>115.3</v>
+      </c>
+      <c r="F5" s="8">
+        <v>4.8600000000000003</v>
+      </c>
+      <c r="G5" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="H5" s="8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A6" s="6">
+        <v>46070</v>
+      </c>
+      <c r="B6" s="7">
+        <v>0.80776620370370367</v>
+      </c>
+      <c r="C6" s="8">
+        <v>-8.2979000000000003</v>
+      </c>
+      <c r="D6" s="8">
+        <v>116.3984</v>
+      </c>
+      <c r="E6" s="10">
+        <v>11.4</v>
+      </c>
+      <c r="F6" s="8">
+        <v>3.64</v>
+      </c>
+      <c r="G6" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="H6" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A7" s="6">
+        <v>46076</v>
+      </c>
+      <c r="B7" s="7">
+        <v>0.4833912037037037</v>
+      </c>
+      <c r="C7" s="8">
+        <v>-9.3000000000000007</v>
+      </c>
+      <c r="D7" s="8">
+        <v>115.6156</v>
+      </c>
+      <c r="E7" s="10">
+        <v>50.3</v>
+      </c>
+      <c r="F7" s="8">
+        <v>4.1100000000000003</v>
+      </c>
+      <c r="G7" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="H7" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="C1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" t="s">
-        <v>3</v>
-      </c>
-      <c r="F1" t="s">
-        <v>4</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8">
-      <c r="A2" s="4">
-        <v>46054</v>
-      </c>
-      <c r="B2" s="3">
-        <v>0.57359953703703703</v>
-      </c>
-      <c r="C2">
-        <v>-8.49</v>
-      </c>
-      <c r="D2">
-        <v>115.66</v>
-      </c>
-      <c r="E2">
-        <v>9</v>
-      </c>
-      <c r="F2">
-        <v>3.5</v>
-      </c>
-      <c r="G2" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="H2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8">
-      <c r="A3" s="4">
-        <v>46069</v>
-      </c>
-      <c r="B3" s="3">
-        <v>0.49935185185185182</v>
-      </c>
-      <c r="C3">
-        <v>-8.6</v>
-      </c>
-      <c r="D3">
-        <v>118.41</v>
-      </c>
-      <c r="E3">
-        <v>114</v>
-      </c>
-      <c r="F3">
-        <v>3.6</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8">
-      <c r="A4" s="4">
-        <v>46070</v>
-      </c>
-      <c r="B4" s="3">
-        <v>0.81943287037037038</v>
-      </c>
-      <c r="C4">
-        <v>-8.2200000000000006</v>
-      </c>
-      <c r="D4">
-        <v>116.39</v>
-      </c>
-      <c r="E4">
-        <v>10</v>
-      </c>
-      <c r="F4">
-        <v>3.5</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8">
-      <c r="A5" s="4">
-        <v>46076</v>
-      </c>
-      <c r="B5" s="3">
-        <v>0.49505787037037036</v>
-      </c>
-      <c r="C5">
-        <v>-9.26</v>
-      </c>
-      <c r="D5">
-        <v>115.65</v>
-      </c>
-      <c r="E5">
-        <v>44</v>
-      </c>
-      <c r="F5">
-        <v>4</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="H5" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8">
-      <c r="A6" s="4">
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A8" s="6">
         <v>46080</v>
       </c>
-      <c r="B6" s="3">
-        <v>0.81824074074074071</v>
-      </c>
-      <c r="C6">
-        <v>-7.79</v>
-      </c>
-      <c r="D6">
-        <v>117.35</v>
-      </c>
-      <c r="E6">
+      <c r="B8" s="7">
+        <v>0.80657407407407411</v>
+      </c>
+      <c r="C8" s="8">
+        <v>-7.7590000000000003</v>
+      </c>
+      <c r="D8" s="8">
+        <v>117.3691</v>
+      </c>
+      <c r="E8" s="10">
+        <v>13.7</v>
+      </c>
+      <c r="F8" s="8">
+        <v>4.45</v>
+      </c>
+      <c r="G8" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="F6">
-        <v>4.7</v>
-      </c>
-      <c r="G6" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="H6" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8">
-      <c r="A7" s="4"/>
-    </row>
-    <row r="8" spans="1:8">
-      <c r="A8" s="4"/>
-    </row>
-    <row r="9" spans="1:8">
-      <c r="A9" s="4"/>
-    </row>
-    <row r="10" spans="1:8">
-      <c r="A10" s="4"/>
-    </row>
-    <row r="11" spans="1:8">
-      <c r="A11" s="4"/>
-    </row>
-    <row r="12" spans="1:8">
-      <c r="A12" s="4"/>
-    </row>
-    <row r="13" spans="1:8">
-      <c r="A13" s="4"/>
-    </row>
-    <row r="14" spans="1:8">
-      <c r="A14" s="4"/>
-    </row>
-    <row r="15" spans="1:8">
-      <c r="A15" s="4"/>
-    </row>
-    <row r="16" spans="1:8">
-      <c r="A16" s="4"/>
-    </row>
-    <row r="17" spans="1:1">
-      <c r="A17" s="4"/>
+      <c r="H8" s="8" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A9" s="3"/>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A10" s="3"/>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A11" s="3"/>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A12" s="3"/>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A13" s="3"/>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A14" s="3"/>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A15" s="3"/>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A16" s="3"/>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A17" s="3"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
